--- a/priv/norm_templates/IT3-TournamentReportForm.xlsx
+++ b/priv/norm_templates/IT3-TournamentReportForm.xlsx
@@ -352,6 +352,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -525,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -654,6 +657,8 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1824,12 +1829,13 @@
       <c r="A6" t="s">
         <v>2</v>
       </c>
+      <c r="B6" s="58"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="12"/>
+      <c r="B7" s="59"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">

--- a/priv/norm_templates/IT3-TournamentReportForm.xlsx
+++ b/priv/norm_templates/IT3-TournamentReportForm.xlsx
@@ -1200,9 +1200,7 @@
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="6" t="s">
-        <v>88</v>
-      </c>
+      <c r="D13" s="6"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>

--- a/priv/norm_templates/IT3-TournamentReportForm.xlsx
+++ b/priv/norm_templates/IT3-TournamentReportForm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Lucdata\schaken\excel\schaken_2019_2020\fide_ecu\formulieren\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aurora/Downloads/brugesmasterscheck/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB0D559-93BC-4A89-B706-FE08B622D906}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370F29D6-3FAB-E84A-9735-BDA9BF907653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaat" sheetId="2" r:id="rId1"/>
@@ -297,9 +297,6 @@
     <t>Tournament Type</t>
   </si>
   <si>
-    <t>Pairing System of a</t>
-  </si>
-  <si>
     <t>Manual</t>
   </si>
   <si>
@@ -346,15 +343,15 @@
   </si>
   <si>
     <t>Please, refer to FIDE Data Protection Policy published in FIDE at https://www.fide.com/privacy.</t>
+  </si>
+  <si>
+    <t>Pairing System</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -528,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -544,26 +541,25 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -573,6 +569,66 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -588,18 +644,6 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -609,56 +653,6 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -677,9 +671,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -717,9 +711,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -752,26 +746,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -804,26 +781,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1001,12 +961,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="10" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24.6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
@@ -1015,7 +975,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -1031,28 +991,28 @@
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="str">
+    <row r="4" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="54" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$1),"",Invulformulier!$B$1)</f>
         <v/>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="56"/>
       <c r="D4" s="7" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$2),"",Invulformulier!$B$2)</f>
         <v/>
       </c>
-      <c r="E4" s="42" t="str">
+      <c r="E4" s="35" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$3),"",Invulformulier!$B$3)</f>
         <v/>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="43"/>
-    </row>
-    <row r="5" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="36"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>85</v>
       </c>
@@ -1070,31 +1030,31 @@
       <c r="I5" s="4"/>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="str">
+    <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$4),"",Invulformulier!$B$4)</f>
         <v/>
       </c>
-      <c r="B6" s="30" t="str">
+      <c r="B6" s="49" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$5),"",Invulformulier!$B$5)</f>
         <v/>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="32" t="str">
+      <c r="C6" s="49"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="51" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$6),"",Invulformulier!$B$6)</f>
         <v/>
       </c>
-      <c r="F6" s="33"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="32" t="str">
+      <c r="F6" s="52"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="51" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$7),"",Invulformulier!$B$7)</f>
         <v/>
       </c>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
-    </row>
-    <row r="7" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
+    </row>
+    <row r="7" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>86</v>
       </c>
@@ -1108,40 +1068,33 @@
       <c r="I7" s="4"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="str">
+    <row r="8" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="29" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$8),"",Invulformulier!$B$8)</f>
         <v/>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="50" t="str">
+      <c r="B8" s="30"/>
+      <c r="C8" s="31" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$9),"",Invulformulier!$B$9)</f>
         <v/>
       </c>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="51"/>
-    </row>
-    <row r="9" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="9" t="s">
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="32"/>
+    </row>
+    <row r="9" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="10"/>
+      <c r="B9" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
-    </row>
-    <row r="10" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="15"/>
       <c r="B10" s="37" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$10),"/",Invulformulier!$B$10)</f>
         <v>/</v>
@@ -1155,7 +1108,7 @@
       <c r="I10" s="37"/>
       <c r="J10" s="38"/>
     </row>
-    <row r="11" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>4</v>
       </c>
@@ -1173,34 +1126,36 @@
       <c r="I11" s="4"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="44" t="str">
+    <row r="12" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="41" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$11),"",Invulformulier!$B$11)</f>
         <v/>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="55" t="str">
+      <c r="B12" s="42"/>
+      <c r="C12" s="46" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$12),"",Invulformulier!$B$12)</f>
         <v/>
       </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="46" t="str">
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="43" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$13),"",Invulformulier!$B$13)</f>
         <v/>
       </c>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="48"/>
-    </row>
-    <row r="13" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="45"/>
+    </row>
+    <row r="13" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>87</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="6"/>
+      <c r="D13" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -1208,79 +1163,79 @@
       <c r="I13" s="4"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="35" t="str">
+    <row r="14" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="29" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$14),"",Invulformulier!$B$14)</f>
         <v/>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="21" t="s">
+      <c r="B14" s="30"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="36" t="str">
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="30" t="str">
         <f>CONCATENATE(IF(ISBLANK(Invulformulier!$B$17),"/",Invulformulier!$B$17)," - ",IF(ISBLANK(Invulformulier!$B$18),"/",Invulformulier!$B$18))</f>
         <v>/ - /</v>
       </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="49"/>
-    </row>
-    <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="35" t="str">
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="39"/>
+    </row>
+    <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="29" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$15),"",Invulformulier!$B$15)</f>
         <v/>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20" t="str">
+      <c r="B15" s="30"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="19" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$19),"/",Invulformulier!$B$19)</f>
         <v>/</v>
       </c>
-      <c r="G15" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" s="19"/>
-      <c r="I15" s="36" t="str">
+      <c r="G15" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="30" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$20),"/",Invulformulier!$B$20)</f>
         <v>/</v>
       </c>
-      <c r="J15" s="49"/>
-    </row>
-    <row r="16" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="52" t="str">
+      <c r="J15" s="39"/>
+    </row>
+    <row r="16" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="33" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$16),"",Invulformulier!$B$16)</f>
         <v/>
       </c>
-      <c r="B16" s="53"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="18" t="str">
+      <c r="B16" s="34"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="17" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$21),"/",Invulformulier!$B$21)</f>
         <v>X</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="53" t="str">
+      <c r="H16" s="16"/>
+      <c r="I16" s="34" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$22),"/",Invulformulier!$B$22)</f>
         <v>/</v>
       </c>
-      <c r="J16" s="54"/>
-    </row>
-    <row r="17" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J16" s="40"/>
+    </row>
+    <row r="17" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -1292,261 +1247,261 @@
       <c r="I17" s="4"/>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="35" t="str">
+    <row r="18" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="29" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$23),"",Invulformulier!$B$23)</f>
         <v/>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="49"/>
-    </row>
-    <row r="19" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="35" t="str">
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="39"/>
+    </row>
+    <row r="19" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="29" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$24),"",Invulformulier!$B$24)</f>
         <v/>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="49"/>
-    </row>
-    <row r="20" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="35" t="str">
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="39"/>
+    </row>
+    <row r="20" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="29" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$25),"",Invulformulier!$B$25)</f>
         <v/>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="49"/>
-    </row>
-    <row r="21" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="52" t="str">
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="39"/>
+    </row>
+    <row r="21" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="33" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$26),"",Invulformulier!$B$26)</f>
         <v/>
       </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="54"/>
-    </row>
-    <row r="22" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="40"/>
+    </row>
+    <row r="22" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="C22" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="D22" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="I22" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="26" t="s">
+      <c r="B23" s="24">
+        <f>Invulformulier!$B$27</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="24">
+        <f>Invulformulier!$B$28</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="24">
+        <f>Invulformulier!$B$29</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="24">
+        <f>Invulformulier!$B$30</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="25">
-        <f>Invulformulier!$B$27</f>
-        <v>0</v>
-      </c>
-      <c r="C23" s="25">
-        <f>Invulformulier!$B$28</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="25">
-        <f>Invulformulier!$B$29</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="25">
-        <f>Invulformulier!$B$30</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="26" t="s">
+      <c r="G23" s="24">
+        <f>Invulformulier!$B$43</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="24">
+        <f>Invulformulier!$B$44</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="24">
+        <f>Invulformulier!$B$45</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="24">
+        <f>Invulformulier!$B$46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="24">
+        <f>Invulformulier!$B$31</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="24">
+        <f>Invulformulier!$B$32</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="24">
+        <f>Invulformulier!$B$33</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="24">
+        <f>Invulformulier!$B$34</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="24">
+        <f>Invulformulier!$B$47</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="24">
+        <f>Invulformulier!$B$48</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="24">
+        <f>Invulformulier!$B$49</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="24">
+        <f>Invulformulier!$B$50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="24">
+        <f>Invulformulier!$B$35</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="24">
+        <f>Invulformulier!$B$36</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="24">
+        <f>Invulformulier!$B$37</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="24">
+        <f>Invulformulier!$B$38</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="24">
+        <f>Invulformulier!$B$51</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="24">
+        <f>Invulformulier!$B$52</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="24">
+        <f>Invulformulier!$B$53</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="24">
+        <f>Invulformulier!$B$54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="24">
+        <f>Invulformulier!$B$39</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="24">
+        <f>Invulformulier!$B$40</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="24">
+        <f>Invulformulier!$B$41</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="24">
+        <f>Invulformulier!$B$42</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="24">
+        <f>Invulformulier!$B$55</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="24">
+        <f>Invulformulier!$B$56</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="24">
+        <f>Invulformulier!$B$57</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="24">
+        <f>Invulformulier!$B$58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="G23" s="25">
-        <f>Invulformulier!$B$43</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="25">
-        <f>Invulformulier!$B$44</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="25">
-        <f>Invulformulier!$B$45</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="25">
-        <f>Invulformulier!$B$46</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="25">
-        <f>Invulformulier!$B$31</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="25">
-        <f>Invulformulier!$B$32</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="25">
-        <f>Invulformulier!$B$33</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="25">
-        <f>Invulformulier!$B$34</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="25">
-        <f>Invulformulier!$B$47</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="25">
-        <f>Invulformulier!$B$48</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="25">
-        <f>Invulformulier!$B$49</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="25">
-        <f>Invulformulier!$B$50</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="25">
-        <f>Invulformulier!$B$35</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="25">
-        <f>Invulformulier!$B$36</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="25">
-        <f>Invulformulier!$B$37</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="25">
-        <f>Invulformulier!$B$38</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="25">
-        <f>Invulformulier!$B$51</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="25">
-        <f>Invulformulier!$B$52</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="25">
-        <f>Invulformulier!$B$53</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="25">
-        <f>Invulformulier!$B$54</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="25">
-        <f>Invulformulier!$B$39</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="25">
-        <f>Invulformulier!$B$40</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="25">
-        <f>Invulformulier!$B$41</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="25">
-        <f>Invulformulier!$B$42</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="25">
-        <f>Invulformulier!$B$55</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="25">
-        <f>Invulformulier!$B$56</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="25">
-        <f>Invulformulier!$B$57</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="25">
-        <f>Invulformulier!$B$58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1558,40 +1513,33 @@
       <c r="I27" s="4"/>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="35" t="str">
+    <row r="28" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="29" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$59),"",Invulformulier!$B$59)</f>
         <v/>
       </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="50" t="str">
+      <c r="B28" s="30"/>
+      <c r="C28" s="31" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$60),"",Invulformulier!$B$60)</f>
         <v/>
       </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="51"/>
-    </row>
-    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="10"/>
-    </row>
-    <row r="30" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="16"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="32"/>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="10"/>
+      <c r="B29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J29" s="9"/>
+    </row>
+    <row r="30" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="15"/>
       <c r="B30" s="37" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$61),"/",Invulformulier!$B$61)</f>
         <v>/</v>
@@ -1605,9 +1553,9 @@
       <c r="I30" s="37"/>
       <c r="J30" s="38"/>
     </row>
-    <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1619,27 +1567,27 @@
       <c r="I31" s="4"/>
       <c r="J31" s="5"/>
     </row>
-    <row r="32" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="35" t="str">
+    <row r="32" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="29" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$62),"",Invulformulier!$B$62)</f>
         <v/>
       </c>
-      <c r="B32" s="36"/>
-      <c r="C32" s="50" t="str">
+      <c r="B32" s="30"/>
+      <c r="C32" s="31" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$63),"",Invulformulier!$B$63)</f>
         <v/>
       </c>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="51"/>
-    </row>
-    <row r="33" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="32"/>
+    </row>
+    <row r="33" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1651,27 +1599,27 @@
       <c r="I33" s="4"/>
       <c r="J33" s="5"/>
     </row>
-    <row r="34" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="35" t="str">
+    <row r="34" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="29" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$64),"",Invulformulier!$B$64)</f>
         <v/>
       </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="50" t="str">
+      <c r="B34" s="30"/>
+      <c r="C34" s="31" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$65),"",Invulformulier!$B$65)</f>
         <v/>
       </c>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="50"/>
-      <c r="J34" s="51"/>
-    </row>
-    <row r="35" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="32"/>
+    </row>
+    <row r="35" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1683,27 +1631,27 @@
       <c r="I35" s="4"/>
       <c r="J35" s="5"/>
     </row>
-    <row r="36" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="35" t="str">
+    <row r="36" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="29" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$66),"",Invulformulier!$B$66)</f>
         <v/>
       </c>
-      <c r="B36" s="36"/>
-      <c r="C36" s="50" t="str">
+      <c r="B36" s="30"/>
+      <c r="C36" s="31" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$67),"",Invulformulier!$B$67)</f>
         <v/>
       </c>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="51"/>
-    </row>
-    <row r="37" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="32"/>
+    </row>
+    <row r="37" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1715,42 +1663,65 @@
       <c r="I37" s="4"/>
       <c r="J37" s="5"/>
     </row>
-    <row r="38" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="52" t="str">
+    <row r="38" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="33" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$68),"",Invulformulier!$B$68)</f>
         <v/>
       </c>
-      <c r="B38" s="53"/>
-      <c r="C38" s="42" t="str">
+      <c r="B38" s="34"/>
+      <c r="C38" s="35" t="str">
         <f>IF(ISBLANK(Invulformulier!$B$69),"",Invulformulier!$B$69)</f>
         <v/>
       </c>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
-      <c r="J38" s="43"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="28" t="str">
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="36"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="27" t="str">
         <f>CONCATENATE("The organizer must provide this report form to each arbiter who has achieved a norm,  ",Invulformulier!$B$70,"  federation, the organizing federation and the FIDE Secretariat.")</f>
         <v>The organizer must provide this report form to each arbiter who has achieved a norm,    federation, the organizing federation and the FIDE Secretariat.</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="29" t="s">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" s="28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="28" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="29" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A21:J21"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:J36"/>
     <mergeCell ref="A38:B38"/>
@@ -1760,29 +1731,6 @@
     <mergeCell ref="C32:J32"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="C34:J34"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="B10:J10"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="H6:J6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="94" orientation="portrait" r:id="rId1"/>
@@ -1792,118 +1740,117 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B70"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="64" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="60.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="58"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="59"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="11"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="14"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="13"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="13"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="12"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="13"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="12"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -1911,279 +1858,279 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <f>B27-B29</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <f>B31-B33</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>26</v>
       </c>
-      <c r="B38" s="27">
+      <c r="B38" s="26">
         <f>B35-B37</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="27">
+      <c r="B42" s="26">
         <f>B39-B41</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="27">
+      <c r="B46" s="26">
         <f>B43-B45</f>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="27">
+      <c r="B50" s="26">
         <f>B47-B49</f>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>42</v>
       </c>
-      <c r="B54" s="27">
+      <c r="B54" s="26">
         <f>B51-B53</f>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>46</v>
       </c>
-      <c r="B58" s="27">
+      <c r="B58" s="26">
         <f>B55-B57</f>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>81</v>
       </c>
